--- a/output/full_scan/batch_seq4_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq4_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1169.734260067438</v>
+        <v>1139.734260067438</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>88.3</v>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3652</v>
+        <v>3537</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>精聯</t>
+          <t>堡達</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1084</v>
+        <v>1108.427758154003</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>40.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>74.21225350807214</v>
+        <v>68.44827638730054</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.92168699764639</v>
+        <v>34.31653859758376</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.103757225226336</v>
+        <v>1.623108782781966</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4398496843376522</v>
+        <v>-0.2502579201540005</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3504</v>
+        <v>3652</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>精聯</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1066.959317927589</v>
+        <v>1084</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>91.2</v>
+        <v>40.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>64.43374608271276</v>
+        <v>74.21225350807214</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>35.6013937900665</v>
+        <v>34.92168699764639</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.727947972843808</v>
+        <v>5.103757225226336</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.6497665569422728</v>
+        <v>0.4398496843376522</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3550</v>
+        <v>3504</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>聯穎</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1028.274185274335</v>
+        <v>1066.959317927589</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>37.25</v>
+        <v>91.2</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>84.98043129241458</v>
+        <v>64.43374608271276</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>43.29118195152705</v>
+        <v>35.6013937900665</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4274185274334906</v>
+        <v>1.727947972843808</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.252352534366074</v>
+        <v>0.6497665569422728</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3296</v>
+        <v>3357</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>勝德</t>
+          <t>臺慶科</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1021.717482152456</v>
+        <v>1051.561219422357</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>29.8</v>
+        <v>348</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>79.61205579633382</v>
+        <v>71.35572502569433</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>35.44149209876501</v>
+        <v>36.94071069503155</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.771748215245578</v>
+        <v>0.8467765293347008</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.781751557479327</v>
+        <v>1.425888439898966</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3357</v>
+        <v>3550</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>聯穎</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1011.561219422357</v>
+        <v>1028.274185274335</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>348</v>
+        <v>37.25</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>71.35572502569433</v>
+        <v>84.98043129241458</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>36.94071069503155</v>
+        <v>43.29118195152705</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8467765293347008</v>
+        <v>0.4274185274334906</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.425888439898966</v>
+        <v>1.252352534366074</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3236</v>
+        <v>3296</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>千如</t>
+          <t>勝德</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>999.8683393763512</v>
+        <v>1021.717482152456</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>71</v>
+        <v>29.8</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>71.69006379246866</v>
+        <v>79.61205579633382</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>42.47013668831245</v>
+        <v>35.44149209876501</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.432503983890229</v>
+        <v>3.771748215245578</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.9325425698481586</v>
+        <v>0.781751557479327</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3189</v>
+        <v>3236</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>千如</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>997.8759261508214</v>
+        <v>1019.868339376351</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>724</v>
+        <v>71</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.22059924130131</v>
+        <v>71.69006379246866</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.6368708377514</v>
+        <v>42.47013668831245</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.670152905712217</v>
+        <v>2.432503983890229</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-8.148041022621413</v>
+        <v>0.9325425698481586</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3605</v>
+        <v>3234</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>宏致</t>
+          <t>光環</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>991.928372485474</v>
+        <v>1004.255296550938</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>80.5</v>
+        <v>145</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.40504478248155</v>
+        <v>66.51092159583662</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23.4615643438507</v>
+        <v>14.60782679118286</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.268081803730047</v>
+        <v>2.121781455979477</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2286681245420385</v>
+        <v>1.473187399113755</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3362</v>
+        <v>3189</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>989.4947257949112</v>
+        <v>997.8759261508214</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>211</v>
+        <v>724</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>82.28167641016225</v>
+        <v>61.22059924130131</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>42.40345911773111</v>
+        <v>21.6368708377514</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.049472579491114</v>
+        <v>1.670152905712217</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>7.140716884345185</v>
+        <v>-8.148041022621413</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3441</v>
+        <v>3605</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>聯一光</t>
+          <t>宏致</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>989.045035149953</v>
+        <v>991.928372485474</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>92.3</v>
+        <v>80.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>82.81528453814417</v>
+        <v>58.40504478248155</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>63.57770411341581</v>
+        <v>23.4615643438507</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.004503514995318</v>
+        <v>2.268081803730047</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.028321017724401</v>
+        <v>0.2286681245420385</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3443</v>
+        <v>3303</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>岱稜</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>970.2839708113796</v>
+        <v>981.2647994331844</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4860</v>
+        <v>61</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.79343457487133</v>
+        <v>71.66261260992458</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.02728698494213</v>
+        <v>32.70050089501994</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.688365920910345</v>
+        <v>0.926479943318436</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>26.51256663401395</v>
+        <v>1.107857401024331</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3234</v>
+        <v>3443</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>964.2552965509382</v>
+        <v>970.2839708113796</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>145</v>
+        <v>4860</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>66.51092159583662</v>
+        <v>55.79343457487133</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14.60782679118286</v>
+        <v>22.02728698494213</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.121781455979477</v>
+        <v>1.688365920910345</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.473187399113755</v>
+        <v>26.51256663401395</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3532</v>
+        <v>3362</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>951.3363401015042</v>
+        <v>959.4947257949112</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>390</v>
+        <v>211</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>69.74080203202783</v>
+        <v>82.28167641016225</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>32.82858333380936</v>
+        <v>42.40345911773111</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.720943706910298</v>
+        <v>2.049472579491114</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>8.120499196715606</v>
+        <v>7.140716884345185</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3303</v>
+        <v>3532</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>岱稜</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>941.2647994331844</v>
+        <v>951.3363401015042</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>61</v>
+        <v>390</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,29 +1400,29 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>71.66261260992458</v>
+        <v>69.74080203202783</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>32.70050089501994</v>
+        <v>32.82858333380936</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.926479943318436</v>
+        <v>1.720943706910298</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.107857401024331</v>
+        <v>8.120499196715606</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>925.0532218840012</v>
+        <v>945.0532218840012</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>3520</v>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>55.1</v>
@@ -1587,21 +1587,21 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3583</v>
+        <v>3290</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>東浦</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>867.9653088568117</v>
+        <v>878.9276710679484</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>889</v>
+        <v>69.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.40190833616759</v>
+        <v>81.9354981983894</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.64147332943562</v>
+        <v>34.53336894941152</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.299544877750179</v>
+        <v>1.492767106794843</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-4.185915908363814</v>
+        <v>1.834012007440438</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3285</v>
+        <v>3465</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>微端</t>
+          <t>進泰電子</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>867.6792417838897</v>
+        <v>875.0044763092618</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>51.2</v>
+        <v>36.3</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>89.56077050607887</v>
+        <v>67.15391076993859</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>48.20691609684711</v>
+        <v>35.55209737591881</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.867924178388972</v>
+        <v>2.022661633826229</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.91234910941802</v>
+        <v>0.5539801413449856</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3530</v>
+        <v>3583</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>晶相光</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>851.758129101786</v>
+        <v>867.9653088568117</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>889</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.47751186122955</v>
+        <v>58.40190833616759</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19.85936583298716</v>
+        <v>20.64147332943562</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.963491955822206</v>
+        <v>1.299544877750179</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.5425553794851505</v>
+        <v>-4.185915908363814</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3450</v>
+        <v>3527</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>聚積</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>842.9167869953504</v>
+        <v>865.697191221058</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>565</v>
+        <v>70.7</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.88492921111789</v>
+        <v>68.61924072313289</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.31876310742621</v>
+        <v>30.49561877310225</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.329637391596367</v>
+        <v>1.295081179359216</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.272755313447206</v>
+        <v>1.281710757269586</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3290</v>
+        <v>3530</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>東浦</t>
+          <t>晶相光</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>838.9276710679484</v>
+        <v>851.758129101786</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>69.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>81.9354981983894</v>
+        <v>61.47751186122955</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.53336894941152</v>
+        <v>19.85936583298716</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.492767106794843</v>
+        <v>3.963491955822206</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.834012007440438</v>
+        <v>0.5425553794851505</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3465</v>
+        <v>3450</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>進泰電子</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>835.0044763092618</v>
+        <v>842.9167869953504</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>36.3</v>
+        <v>565</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,29 +1877,29 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>67.15391076993859</v>
+        <v>63.88492921111789</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>35.55209737591881</v>
+        <v>31.31876310742621</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.022661633826229</v>
+        <v>1.329637391596367</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.5539801413449856</v>
+        <v>-1.272755313447206</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>815.9091659330617</v>
+        <v>835.9091659330617</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>21.85</v>
@@ -1958,21 +1958,21 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3406</v>
+        <v>3516</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>亞帝歐</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>795.3884138069189</v>
+        <v>830.0129883361029</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>753</v>
+        <v>27.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>67.54015755068144</v>
+        <v>72.18388057412918</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45.97904286733423</v>
+        <v>38.49553823431459</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.116971017590333</v>
+        <v>1.084802545181269</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,11 +2001,11 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>6.968626782752523</v>
+        <v>0.3687366219436336</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>788.7979232387238</v>
+        <v>828.7979232387238</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>16.25</v>
@@ -2064,21 +2064,21 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3321</v>
+        <v>3479</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>同泰</t>
+          <t>安勤</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>782.6611228265052</v>
+        <v>810.3795141339524</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>24.3</v>
+        <v>136.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>73.2014522401325</v>
+        <v>66.10055765835635</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>33.18726673083063</v>
+        <v>47.15219839461889</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9395670821979692</v>
+        <v>1.058758265734219</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3710629673034309</v>
+        <v>-0.8510492249076842</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3479</v>
+        <v>3406</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安勤</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>770.3795141339524</v>
+        <v>795.3884138069189</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>136.5</v>
+        <v>753</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>66.10055765835635</v>
+        <v>67.54015755068144</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>47.15219839461889</v>
+        <v>45.97904286733423</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.058758265734219</v>
+        <v>1.116971017590333</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.8510492249076842</v>
+        <v>6.968626782752523</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3535</v>
+        <v>3321</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>同泰</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>765.1749186521466</v>
+        <v>782.6611228265052</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>134</v>
+        <v>24.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>54.7825619715267</v>
+        <v>73.2014522401325</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.6552009339419</v>
+        <v>33.18726673083063</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3335928392618735</v>
+        <v>0.9395670821979692</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3102433054051203</v>
+        <v>0.3710629673034309</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3312</v>
+        <v>3535</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>弘憶股</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>754.276320893093</v>
+        <v>765.1749186521466</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>62.8</v>
+        <v>134</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>61.18691602626438</v>
+        <v>54.7825619715267</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>38.91409108528269</v>
+        <v>21.6552009339419</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>3.024021348522256</v>
+        <v>0.3335928392618735</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.5106813553166667</v>
+        <v>0.3102433054051203</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3356</v>
+        <v>3312</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>奇偶</t>
+          <t>弘憶股</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>736.6258853827551</v>
+        <v>754.276320893093</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>60.4</v>
+        <v>62.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.67041282445467</v>
+        <v>61.18691602626438</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>25.59893450540328</v>
+        <v>38.91409108528269</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.290457103053036</v>
+        <v>3.024021348522256</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.3057811834384178</v>
+        <v>-0.5106813553166667</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3545</v>
+        <v>3455</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>敦泰</t>
+          <t>由田</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>728.8282487634705</v>
+        <v>738.260833655517</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.43165851626119</v>
+        <v>52.68053843949318</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.05868521446326</v>
+        <v>21.7999167571623</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.8073133471894965</v>
+        <v>0.7048516285377946</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.09856862664033279</v>
+        <v>0.1288738189717388</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3673</v>
+        <v>3356</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>奇偶</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>710.1834309725426</v>
+        <v>736.6258853827551</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>86.2</v>
+        <v>60.4</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.03720846503185</v>
+        <v>53.67041282445467</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>30.27014285732591</v>
+        <v>25.59893450540328</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9876464729410984</v>
+        <v>1.290457103053036</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.055841476517706</v>
+        <v>-0.3057811834384178</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3653</v>
+        <v>3221</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台嘉碩</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>699.9261034067349</v>
+        <v>734.8795384465431</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>3965</v>
+        <v>60.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.51848377503938</v>
+        <v>57.91080736421272</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15.9745170357895</v>
+        <v>28.47228956834324</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.090638571765712</v>
+        <v>0.3674485496913019</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>46.77502261502399</v>
+        <v>-0.4119978428814352</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3455</v>
+        <v>3213</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>由田</t>
+          <t>茂訊</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>698.260833655517</v>
+        <v>729.680202712461</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>242</v>
+        <v>134</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.68053843949318</v>
+        <v>62.00537096066127</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.7999167571623</v>
+        <v>46.9979094625696</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7048516285377946</v>
+        <v>0.2637106153229251</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1288738189717388</v>
+        <v>-0.0885936732147172</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3715</v>
+        <v>3545</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>敦泰</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>697.5175655570887</v>
+        <v>728.8282487634705</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>179</v>
+        <v>58</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.63301549831363</v>
+        <v>55.43165851626119</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.47180245597881</v>
+        <v>20.05868521446326</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.013591817284832</v>
+        <v>0.8073133471894965</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.965219152810982</v>
+        <v>-0.09856862664033279</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3221</v>
+        <v>3374</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>台嘉碩</t>
+          <t>精材</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>694.8795384465431</v>
+        <v>717.767596083473</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>60.5</v>
+        <v>251</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>57.91080736421272</v>
+        <v>55.14621367712048</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.47228956834324</v>
+        <v>16.59789677399097</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3674485496913019</v>
+        <v>0.5319200517445491</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.4119978428814352</v>
+        <v>-2.025752642307652</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>3213</v>
+        <v>3673</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>茂訊</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>689.680202712461</v>
+        <v>710.1834309725426</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>134</v>
+        <v>86.2</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>62.00537096066127</v>
+        <v>59.03720846503185</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46.9979094625696</v>
+        <v>30.27014285732591</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2637106153229251</v>
+        <v>0.9876464729410984</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0885936732147172</v>
+        <v>-1.055841476517706</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>3374</v>
+        <v>3653</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>精材</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>677.767596083473</v>
+        <v>699.9261034067349</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>251</v>
+        <v>3965</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.14621367712048</v>
+        <v>53.51848377503938</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16.59789677399097</v>
+        <v>15.9745170357895</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5319200517445491</v>
+        <v>1.090638571765712</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.025752642307652</v>
+        <v>46.77502261502399</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>3311</v>
+        <v>3715</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>676.5141195314453</v>
+        <v>697.5175655570887</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>38.75</v>
+        <v>179</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.40134133762294</v>
+        <v>54.63301549831363</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>31.64714752116312</v>
+        <v>11.47180245597881</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3728629492124184</v>
+        <v>1.013591817284832</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0414228737400463</v>
+        <v>0.965219152810982</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>3711</v>
+        <v>3289</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>宜特</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>675.1206596361726</v>
+        <v>692.1529531832897</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>613</v>
+        <v>174.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>60.01670631459559</v>
+        <v>53.62247072775415</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.21670048269508</v>
+        <v>12.74562118895533</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.377093494196537</v>
+        <v>0.5656024273230892</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.870579387250778</v>
+        <v>0.3229314180520839</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3289</v>
+        <v>3520</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宜特</t>
+          <t>華盈</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>672.1529531832897</v>
+        <v>680.5853687716832</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>174.5</v>
+        <v>17.1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.62247072775415</v>
+        <v>58.66898536962894</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12.74562118895533</v>
+        <v>36.87164298453401</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5656024273230892</v>
+        <v>0.3265714019690225</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.3229314180520839</v>
+        <v>0.0335942946006724</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3322</v>
+        <v>3311</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>建舜電</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>656.151206057726</v>
+        <v>676.5141195314453</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>14.85</v>
+        <v>38.75</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.95185638790891</v>
+        <v>57.40134133762294</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.46528265446252</v>
+        <v>31.64714752116312</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5036263115954455</v>
+        <v>0.3728629492124184</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0487528750957759</v>
+        <v>-0.0414228737400463</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>3257</v>
+        <v>3711</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>虹冠電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>653.0329664755311</v>
+        <v>675.1206596361726</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>61.1</v>
+        <v>613</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>58.07455276303951</v>
+        <v>60.01670631459559</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.54682031175446</v>
+        <v>24.21670048269508</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.192292326184736</v>
+        <v>1.377093494196537</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.3038744763815182</v>
+        <v>-1.870579387250778</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3704</v>
+        <v>3264</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>643.5037885569942</v>
+        <v>666.6280972018036</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>48.25</v>
+        <v>232.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>61.18388886135815</v>
+        <v>55.26631799079261</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>35.7071702040239</v>
+        <v>19.02244928889416</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7288484814652415</v>
+        <v>1.249683976975387</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.2156559386036596</v>
+        <v>-0.9954853631385828</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>3168</v>
+        <v>3322</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>眾福科</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>640.7744771980168</v>
+        <v>656.151206057726</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>48</v>
+        <v>14.85</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.84815035769972</v>
+        <v>55.95185638790891</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>27.04873162096323</v>
+        <v>22.46528265446252</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.930978217538689</v>
+        <v>0.5036263115954455</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.12861111571842</v>
+        <v>0.0487528750957759</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3264</v>
+        <v>3313</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>斐成</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>626.6280972018036</v>
+        <v>654.0070627818537</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>232.5</v>
+        <v>12.15</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.26631799079261</v>
+        <v>57.39549603537576</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19.02244928889416</v>
+        <v>22.66296786525641</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.249683976975387</v>
+        <v>1.023781114163805</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.9954853631385828</v>
+        <v>0.093607542397231</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>3211</v>
+        <v>3257</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>虹冠電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>626.5792163765569</v>
+        <v>653.0329664755311</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>436</v>
+        <v>61.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>55.51428232900758</v>
+        <v>58.07455276303951</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.58181849098126</v>
+        <v>16.54682031175446</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4933147364276369</v>
+        <v>1.192292326184736</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.270665903578962</v>
+        <v>-0.3038744763815182</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3607</v>
+        <v>3152</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>谷崧</t>
+          <t>璟德</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>620.6586282717033</v>
+        <v>649.0612159344435</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>16.85</v>
+        <v>204</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>57.4837179497814</v>
+        <v>56.63694301884845</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>26.22466320126953</v>
+        <v>33.51089901966196</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3630239991317452</v>
+        <v>0.5654750987486166</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0264846596536402</v>
+        <v>0.8615197865943394</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>3617</v>
+        <v>3704</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>616.3221605431658</v>
+        <v>643.5037885569942</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>211.5</v>
+        <v>48.25</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.7136109743269</v>
+        <v>61.18388886135815</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>28.95134203381188</v>
+        <v>35.7071702040239</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4102866811797901</v>
+        <v>0.7288484814652415</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.044612515183404</v>
+        <v>-0.2156559386036596</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>3313</v>
+        <v>3168</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>斐成</t>
+          <t>眾福科</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>614.0070627818537</v>
+        <v>640.7744771980168</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>12.15</v>
+        <v>48</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>57.39549603537576</v>
+        <v>52.84815035769972</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.66296786525641</v>
+        <v>27.04873162096323</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.023781114163805</v>
+        <v>0.930978217538689</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.093607542397231</v>
+        <v>-0.12861111571842</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>3294</v>
+        <v>3402</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>610.2830271067497</v>
+        <v>636.7954485698896</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>39.7</v>
+        <v>140.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>56.2530380113101</v>
+        <v>50.50987911994096</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>28.86549561504672</v>
+        <v>13.3075517485461</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5767722791840177</v>
+        <v>0.3732278589142175</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1585824945551448</v>
+        <v>-0.4482912867473043</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>3152</v>
+        <v>3265</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>璟德</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>609.0612159344435</v>
+        <v>630.3946448089537</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>204</v>
+        <v>189.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>56.63694301884845</v>
+        <v>57.96083565037009</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>33.51089901966196</v>
+        <v>16.08072482089561</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5654750987486166</v>
+        <v>1.459051222536956</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.8615197865943394</v>
+        <v>-0.596504010633102</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>3706</v>
+        <v>3485</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>敘豐</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>605.2399069766376</v>
+        <v>621.8995621370286</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>311</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.94043672283206</v>
+        <v>49.0253011311821</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.05107743764978</v>
+        <v>15.77583112013243</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2933546343908959</v>
+        <v>0.460732970422917</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.7584941993304326</v>
+        <v>-4.496151149082399</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>3413</v>
+        <v>3607</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>谷崧</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>604.2808253843693</v>
+        <v>620.6586282717033</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>324.5</v>
+        <v>16.85</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.75336500078447</v>
+        <v>57.4837179497814</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10.19069000081856</v>
+        <v>26.22466320126953</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6387276522199031</v>
+        <v>0.3630239991317452</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.141763040614987</v>
+        <v>-0.0264846596536402</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>3402</v>
+        <v>3617</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>596.7954485698896</v>
+        <v>616.3221605431658</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>140.5</v>
+        <v>211.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.50987911994096</v>
+        <v>54.7136109743269</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.3075517485461</v>
+        <v>28.95134203381188</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3732278589142175</v>
+        <v>0.4102866811797901</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>1</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.4482912867473043</v>
+        <v>-1.044612515183404</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>3265</v>
+        <v>3511</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>矽瑪</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>590.3946448089537</v>
+        <v>610.9768564610548</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>189.5</v>
+        <v>24.95</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>57.96083565037009</v>
+        <v>59.38775368574844</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.08072482089561</v>
+        <v>25.50006066076058</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.459051222536956</v>
+        <v>0.5701569516914191</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>1</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.596504010633102</v>
+        <v>0.0366487024006418</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>3130</v>
+        <v>3706</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>584.4021152340758</v>
+        <v>605.2399069766376</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>224</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>56.74660627079684</v>
+        <v>49.94043672283206</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>23.19613321910795</v>
+        <v>14.05107743764978</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.3656191441649</v>
+        <v>0.2933546343908959</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.298198740155537</v>
+        <v>-0.7584941993304326</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>3485</v>
+        <v>3413</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>敘豐</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>581.8995621370286</v>
+        <v>604.2808253843693</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>311</v>
+        <v>324.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>49.0253011311821</v>
+        <v>53.75336500078447</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.77583112013243</v>
+        <v>10.19069000081856</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.460732970422917</v>
+        <v>0.6387276522199031</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-4.496151149082399</v>
+        <v>1.141763040614987</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>3339</v>
+        <v>3390</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>旭軟</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>581.0024092145862</v>
+        <v>599.8499946576225</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>49.7</v>
+        <v>28.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>53.211017663478</v>
+        <v>54.28797202004589</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.78357770911224</v>
+        <v>18.72832865286058</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.142693608788478</v>
+        <v>0.4586611549272093</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.4563555942750503</v>
+        <v>-0.0117967784519977</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>3438</v>
+        <v>3211</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>類比科</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>573.3332498488114</v>
+        <v>596.5792163765569</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>436</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>57.60802196137174</v>
+        <v>55.51428232900758</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>34.57331687178297</v>
+        <v>20.58181849098126</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9064882188171554</v>
+        <v>0.4933147364276369</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.7189235755847396</v>
+        <v>-1.270665903578962</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>3308</v>
+        <v>3130</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>聯德</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>573.0413206277434</v>
+        <v>584.4021152340758</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>21.45</v>
+        <v>224</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>54.43254414359926</v>
+        <v>56.74660627079684</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>17.67332167502379</v>
+        <v>23.19613321910795</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.12561366765115</v>
+        <v>1.3656191441649</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0111058745468716</v>
+        <v>0.298198740155537</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>3661</v>
+        <v>3294</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>英濟</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>569.0641320048452</v>
+        <v>580.2830271067497</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>4380</v>
+        <v>39.7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.31342478288499</v>
+        <v>56.2530380113101</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.67313281538021</v>
+        <v>28.86549561504672</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.326361160666194</v>
+        <v>0.5767722791840177</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-23.42273471352297</v>
+        <v>-0.1585824945551448</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>3528</v>
+        <v>3141</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>安馳</t>
+          <t>晶宏</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>562.6242396034572</v>
+        <v>574.6963759853471</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>110.5</v>
+        <v>74</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.96715523155476</v>
+        <v>59.24401709007756</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>38.69360179784674</v>
+        <v>32.54246698131355</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.202246264291076</v>
+        <v>0.4920265461257105</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-2.683739721507182</v>
+        <v>-1.260672815793483</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>3390</v>
+        <v>3308</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>旭軟</t>
+          <t>聯德</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>559.8499946576225</v>
+        <v>573.0413206277434</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>28.5</v>
+        <v>21.45</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>54.28797202004589</v>
+        <v>54.43254414359926</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.72832865286058</v>
+        <v>17.67332167502379</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4586611549272093</v>
+        <v>1.12561366765115</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>2</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0117967784519977</v>
+        <v>0.0111058745468716</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>3231</v>
+        <v>3661</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>545.5206866928133</v>
+        <v>569.0641320048452</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>161.5</v>
+        <v>4380</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,49 +4156,49 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.61872254309973</v>
+        <v>51.31342478288499</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.78075674907542</v>
+        <v>16.67313281538021</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5808171881741245</v>
+        <v>1.326361160666194</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.515576065470876</v>
+        <v>-23.42273471352297</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>3702</v>
+        <v>3227</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>543.5243872521011</v>
+        <v>568.018357329979</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.88597649471387</v>
+        <v>54.65616247566889</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>29.88152407820609</v>
+        <v>22.52555536618153</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.384029777813852</v>
+        <v>1.02407092060969</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.209180344764976</v>
+        <v>-1.05286848996511</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>3701</v>
+        <v>3528</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>大眾控</t>
+          <t>安馳</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>540.278435649535</v>
+        <v>562.6242396034572</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>48.45</v>
+        <v>110.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.52392496014613</v>
+        <v>48.96715523155476</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>28.99427356027541</v>
+        <v>38.69360179784674</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4787210057100937</v>
+        <v>2.202246264291076</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.3745155726954632</v>
+        <v>-2.683739721507182</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>3141</v>
+        <v>3349</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>晶宏</t>
+          <t>寶德</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>534.6963759853471</v>
+        <v>558.4034978985208</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>74</v>
+        <v>18.25</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>59.24401709007756</v>
+        <v>36.58453460768563</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>32.54246698131355</v>
+        <v>37.21297332875142</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4920265461257105</v>
+        <v>4.057585438356957</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>2</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.260672815793483</v>
+        <v>0.3220938744267623</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>3576</v>
+        <v>3526</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>聯合再生</t>
+          <t>凡甲</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>534.5601654708255</v>
+        <v>553.4369276638211</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>18</v>
+        <v>327</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>48.78784231777858</v>
+        <v>41.74240694300479</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.37572929498045</v>
+        <v>26.58434521341044</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.138685626212481</v>
+        <v>1.082957699248297</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0736584118205786</v>
+        <v>-6.868526163161791</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>3227</v>
+        <v>3339</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>泰谷</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>528.018357329979</v>
+        <v>551.0024092145862</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>225</v>
+        <v>49.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>54.65616247566889</v>
+        <v>53.211017663478</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>22.52555536618153</v>
+        <v>12.78357770911224</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.02407092060969</v>
+        <v>1.142693608788478</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.05286848996511</v>
+        <v>0.4563555942750503</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>3169</v>
+        <v>3231</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>亞信</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>525.0986229227875</v>
+        <v>545.5206866928133</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>109.5</v>
+        <v>161.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,49 +4474,49 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.34929806257246</v>
+        <v>53.61872254309973</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.54190734276091</v>
+        <v>17.78075674907542</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.1828693493846699</v>
+        <v>0.5808171881741245</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-1.041354796059931</v>
+        <v>-1.515576065470876</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3305</v>
+        <v>3169</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>昇貿</t>
+          <t>亞信</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>524.9386966090972</v>
+        <v>545.0986229227875</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>146</v>
+        <v>109.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>53.04416100490453</v>
+        <v>48.34929806257246</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>24.53915538603288</v>
+        <v>20.54190734276091</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3317957290401144</v>
+        <v>0.1828693493846699</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-2.439977619547772</v>
+        <v>-1.041354796059931</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3349</v>
+        <v>3702</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>寶德</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>518.4034978985208</v>
+        <v>543.5243872521011</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>18.25</v>
+        <v>112</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>36.58453460768563</v>
+        <v>51.88597649471387</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>37.21297332875142</v>
+        <v>29.88152407820609</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4.057585438356957</v>
+        <v>1.384029777813852</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>2</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3220938744267623</v>
+        <v>-1.209180344764976</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3592</v>
+        <v>3438</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎</t>
+          <t>類比科</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>516.3232382851982</v>
+        <v>543.3332498488114</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>275</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>55.56187299420397</v>
+        <v>57.60802196137174</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.97011639462706</v>
+        <v>34.57331687178297</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.237805567856703</v>
+        <v>0.9064882188171554</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>2</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.8950407787755337</v>
+        <v>-0.7189235755847396</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>3135</v>
+        <v>3701</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>大眾控</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>511.2782565333823</v>
+        <v>540.278435649535</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>198</v>
+        <v>48.45</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.0527259120814</v>
+        <v>37.52392496014613</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>24.55571288444758</v>
+        <v>28.99427356027541</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5857696845465105</v>
+        <v>0.4787210057100937</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-6.822998733710874</v>
+        <v>-0.3745155726954632</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>3515</v>
+        <v>3491</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>505.5675603425064</v>
+        <v>537.1314449626195</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>246.5</v>
+        <v>1560</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,49 +4739,49 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.73639292553213</v>
+        <v>37.95776738271167</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>14.97478546950479</v>
+        <v>20.31337716101764</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3457834497165183</v>
+        <v>0.8752327717322819</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-1.002902406712987</v>
+        <v>-54.63709753707519</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>3444</v>
+        <v>3576</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>利機</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>503.9675036147574</v>
+        <v>534.5601654708255</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>18</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>52.54984499908755</v>
+        <v>48.78784231777858</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.85702134104827</v>
+        <v>23.37572929498045</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5537605917792191</v>
+        <v>1.138685626212481</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-1.578901214396271</v>
+        <v>0.0736584118205786</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>3338</v>
+        <v>3305</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>泰碩</t>
+          <t>昇貿</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>499.1323529129306</v>
+        <v>524.9386966090972</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>75.2</v>
+        <v>146</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.72609120898866</v>
+        <v>53.04416100490453</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21.58335629588077</v>
+        <v>24.53915538603288</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3042951555160811</v>
+        <v>0.3317957290401144</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.7798586535239458</v>
+        <v>-2.439977619547772</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>3491</v>
+        <v>3592</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>瑞鼎</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>497.1314449626196</v>
+        <v>516.3232382851982</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1560</v>
+        <v>275</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,49 +4898,49 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>37.95776738271167</v>
+        <v>55.56187299420397</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.31337716101764</v>
+        <v>16.97011639462706</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8752327717322819</v>
+        <v>1.237805567856703</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-54.63709753707519</v>
+        <v>-0.8950407787755337</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>3229</v>
+        <v>3135</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>晟鈦</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>493.8041783671196</v>
+        <v>511.2782565333823</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>45.75</v>
+        <v>198</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>54.54526628798214</v>
+        <v>47.0527259120814</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>28.13152341916158</v>
+        <v>24.55571288444758</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5084334598758594</v>
+        <v>0.5857696845465105</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.4975397592039023</v>
+        <v>-6.822998733710874</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>3288</v>
+        <v>3306</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>點晶</t>
+          <t>鼎天</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>487.586609296503</v>
+        <v>505.9271339353466</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>20.9</v>
+        <v>48</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.10685013374336</v>
+        <v>54.07048576692558</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>26.83427814458225</v>
+        <v>17.65832878332387</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.788437580339859</v>
+        <v>0.5695031737458016</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1438467231394373</v>
+        <v>0.0053479822535203</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>3207</v>
+        <v>3515</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>耀勝</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>479.2159515873852</v>
+        <v>505.5675603425064</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>246.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>57.50274998007662</v>
+        <v>52.73639292553213</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21.5392406282254</v>
+        <v>14.97478546950479</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.433147970605748</v>
+        <v>0.3457834497165183</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0790555159360402</v>
+        <v>-1.002902406712987</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>3306</v>
+        <v>3444</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>鼎天</t>
+          <t>利機</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>465.9271339353466</v>
+        <v>503.9675036147574</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>48</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>54.07048576692558</v>
+        <v>52.54984499908755</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.65832878332387</v>
+        <v>24.85702134104827</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5695031737458016</v>
+        <v>0.5537605917792191</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,11 +5128,11 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0053479822535203</v>
+        <v>-1.578901214396271</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>463.5648438719829</v>
+        <v>503.5648438719829</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>33.55</v>
@@ -5191,21 +5191,21 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>3209</v>
+        <v>3498</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>陽程</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>460.3470904866691</v>
+        <v>501.8487946271031</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>62.3</v>
+        <v>123</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.27263021172026</v>
+        <v>47.93526397928229</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>32.82556219686477</v>
+        <v>26.34382831934001</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5513574932616642</v>
+        <v>0.5482007609352203</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-2.302058937601311</v>
+        <v>-3.561773967519628</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>3332</v>
+        <v>3338</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>幸康</t>
+          <t>泰碩</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>458.7811057905055</v>
+        <v>499.1323529129306</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>65</v>
+        <v>75.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.79508917910991</v>
+        <v>49.72609120898866</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>32.67947560540557</v>
+        <v>21.58335629588077</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.0187411657413719</v>
+        <v>0.3042951555160811</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,51 +5287,51 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.3309058224196635</v>
+        <v>-0.7798586535239458</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>3454</v>
+        <v>3229</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>晶睿</t>
+          <t>晟鈦</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>456.3789192122704</v>
+        <v>493.8041783671196</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>80.8</v>
+        <v>45.75</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G92" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>4.286337516643911</v>
+        <v>54.54526628798214</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>58.10940552487618</v>
+        <v>28.13152341916158</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.1127673925682696</v>
+        <v>0.5084334598758594</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,11 +5340,11 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-1.353741975037447</v>
+        <v>-0.4975397592039023</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>452.9558320960602</v>
+        <v>492.9558320960602</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>64.3</v>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3533</v>
+        <v>3207</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>耀勝</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>443.3348698458983</v>
+        <v>479.2159515873852</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>2290</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.96742092565732</v>
+        <v>57.50274998007662</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20.63932701382569</v>
+        <v>21.5392406282254</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8339717689158118</v>
+        <v>1.433147970605748</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-16.3530557068392</v>
+        <v>0.0790555159360402</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3483</v>
+        <v>3324</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>力致</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>438.0891083700661</v>
+        <v>473.9110335876802</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>93.8</v>
+        <v>1070</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>49.70747841230337</v>
+        <v>50.29226328948674</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.5311508451487</v>
+        <v>11.80125053232934</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2957138164463975</v>
+        <v>0.3830474333624553</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.981394320085766</v>
+        <v>-5.703972259370906</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>3324</v>
+        <v>3276</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>宇環</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>433.9110335876802</v>
+        <v>465.8287748211002</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1070</v>
+        <v>15.2</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.29226328948674</v>
+        <v>56.94913822363846</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.80125053232934</v>
+        <v>17.85838422426463</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3830474333624553</v>
+        <v>0.9043372555723336</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-5.703972259370906</v>
+        <v>0.1043708562731059</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3276</v>
+        <v>3209</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>宇環</t>
+          <t>全科</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>425.8287748211002</v>
+        <v>460.3470904866691</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>15.2</v>
+        <v>62.3</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>56.94913822363846</v>
+        <v>42.27263021172026</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.85838422426463</v>
+        <v>32.82556219686477</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9043372555723336</v>
+        <v>0.5513574932616642</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1043708562731059</v>
+        <v>-2.302058937601311</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3665</v>
+        <v>3288</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>點晶</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>424.8408158198552</v>
+        <v>457.586609296503</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>2100</v>
+        <v>20.9</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,69 +5640,69 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>49.80171175605035</v>
+        <v>54.10685013374336</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.65827815261372</v>
+        <v>26.83427814458225</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.300392448114092</v>
+        <v>0.788437580339859</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>28.77563220406348</v>
+        <v>-0.1438467231394373</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3138</v>
+        <v>3454</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>晶睿</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>423.2134644016387</v>
+        <v>456.3789192122704</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>136.5</v>
+        <v>80.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G99" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>32.91438384648461</v>
+        <v>4.286337516643911</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>23.42416849631069</v>
+        <v>58.10940552487618</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3850851394741131</v>
+        <v>0.1127673925682696</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-2.318049432538899</v>
+        <v>-1.353741975037447</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>3419</v>
+        <v>3533</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>譁裕</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>416.5298160676335</v>
+        <v>443.3348698458983</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>14.4</v>
+        <v>2290</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.13926305192287</v>
+        <v>43.96742092565732</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.3307983620914</v>
+        <v>20.63932701382569</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6461679160352651</v>
+        <v>0.8339717689158118</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0883313249237435</v>
+        <v>-16.3530557068392</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>3501</v>
+        <v>3206</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>維熹</t>
+          <t>志豐</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>412.0129351204989</v>
+        <v>438.290475022127</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>41.8</v>
+        <v>38.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.06297129481376</v>
+        <v>52.0943965890819</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>21.89385262013549</v>
+        <v>15.18903496656219</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.544729610214874</v>
+        <v>0.3774242575136287</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.2981183519695137</v>
+        <v>-0.1396098915532296</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>3206</v>
+        <v>3512</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>志豐</t>
+          <t>皇龍</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>398.290475022127</v>
+        <v>435.329104986024</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>38.5</v>
+        <v>20.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>52.0943965890819</v>
+        <v>52.76023380130691</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.18903496656219</v>
+        <v>31.85812819889069</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3774242575136287</v>
+        <v>1.336670793411259</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1396098915532296</v>
+        <v>0.04823348871678</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>3363</v>
+        <v>3523</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>397.5165371769962</v>
+        <v>433.3228175852735</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>712</v>
+        <v>16.55</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.70182813571506</v>
+        <v>52.89821432279106</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>20.73953138332413</v>
+        <v>13.38272490622699</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7929977644448646</v>
+        <v>0.3109108855761686</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,11 +5923,11 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-16.15721640819562</v>
+        <v>-0.3491173357247432</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>393.3113705947444</v>
+        <v>433.3113705947444</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>92.40000000000001</v>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>3490</v>
+        <v>3332</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>單井</t>
+          <t>幸康</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>390.6261650678609</v>
+        <v>428.7811057905055</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>32.45</v>
+        <v>65</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.09742926204422</v>
+        <v>50.79508917910991</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>25.67980493375254</v>
+        <v>32.67947560540557</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3911231247069854</v>
+        <v>0.0187411657413719</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.7390539447935676</v>
+        <v>-0.3309058224196635</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>3714</v>
+        <v>3260</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>390.5449983109327</v>
+        <v>428.4413888779513</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>67.2</v>
+        <v>423</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>48.803609520141</v>
+        <v>51.26150668485789</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.21749340858833</v>
+        <v>10.03080606893492</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4950649985522865</v>
+        <v>0.6857314065002372</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>2</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.4914350395162428</v>
+        <v>-0.8466084609891823</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>3563</v>
+        <v>3228</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>牧德</t>
+          <t>金麗科</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>390.1078203884244</v>
+        <v>427.3835375744979</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>715</v>
+        <v>183.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>38.20539897678859</v>
+        <v>48.73941331327723</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>28.73468919902918</v>
+        <v>17.91990479680177</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4948351461813322</v>
+        <v>0.5773329949096966</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-7.07557053873299</v>
+        <v>-0.3023444131461765</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>3260</v>
+        <v>3665</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>388.4413888779513</v>
+        <v>424.8408158198552</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>423</v>
+        <v>2100</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,49 +6170,49 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.26150668485789</v>
+        <v>49.80171175605035</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10.03080606893492</v>
+        <v>15.65827815261372</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6857314065002372</v>
+        <v>2.300392448114092</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.8466084609891823</v>
+        <v>28.77563220406348</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>3228</v>
+        <v>3138</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>金麗科</t>
+          <t>耀登</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>387.3835375744979</v>
+        <v>423.2134644016387</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>183.5</v>
+        <v>136.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.73941331327723</v>
+        <v>32.91438384648461</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.91990479680177</v>
+        <v>23.42416849631069</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5773329949096966</v>
+        <v>0.3850851394741131</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.3023444131461765</v>
+        <v>-2.318049432538899</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>3694</v>
+        <v>3419</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>海華</t>
+          <t>譁裕</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>380.7330834021102</v>
+        <v>416.5298160676335</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>60.8</v>
+        <v>14.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.65218138624478</v>
+        <v>52.13926305192287</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>22.68336638757079</v>
+        <v>14.3307983620914</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7305452681799839</v>
+        <v>0.6461679160352651</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,11 +6294,11 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.802639713363772</v>
+        <v>0.0883313249237435</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>375.757489116492</v>
+        <v>415.757489116492</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>20.4</v>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3310</v>
+        <v>3501</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>佳穎</t>
+          <t>維熹</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>368.4651953339516</v>
+        <v>412.0129351204989</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>65.8</v>
+        <v>41.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>37.85204496604067</v>
+        <v>46.06297129481376</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.70919288382499</v>
+        <v>21.89385262013549</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.045319416789568</v>
+        <v>1.544729610214874</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.651981475065126</v>
+        <v>0.2981183519695137</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>3380</v>
+        <v>3310</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>明泰</t>
+          <t>佳穎</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>365.5888163627444</v>
+        <v>408.4651953339516</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>34.95</v>
+        <v>65.8</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.59324281119195</v>
+        <v>37.85204496604067</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.3735304449494</v>
+        <v>24.70919288382499</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7190149258182617</v>
+        <v>0.045319416789568</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2107163923609641</v>
+        <v>-0.651981475065126</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3416</v>
+        <v>3529</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>融程電</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>362.5467921930241</v>
+        <v>408.4226053369069</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>176</v>
+        <v>3270</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,49 +6488,49 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>52.06296708975356</v>
+        <v>46.41695008804407</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.87939687907937</v>
+        <v>23.87576545170255</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3697577894850776</v>
+        <v>0.585827754049596</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-1.289376063574811</v>
+        <v>-2.647285676981383</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3191</v>
+        <v>3483</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>雲嘉南</t>
+          <t>力致</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>359.2716278551086</v>
+        <v>408.0891083700661</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>19.35</v>
+        <v>93.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>52.18343929384298</v>
+        <v>49.70747841230337</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>14.89285229231896</v>
+        <v>20.5311508451487</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4069120254139642</v>
+        <v>0.2957138164463975</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>1</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.4923849567954264</v>
+        <v>-0.981394320085766</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>3376</v>
+        <v>3541</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>西柏</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>351.0884935582716</v>
+        <v>400.9504295424908</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>205</v>
+        <v>21.95</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>47.12031839361605</v>
+        <v>41.69380536760393</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.96166975510926</v>
+        <v>38.93912105066922</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.3715033286847038</v>
+        <v>0.5041148247303151</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-2.529157980788407</v>
+        <v>0.0056456284304826</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>3219</v>
+        <v>3490</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>倚強股份</t>
+          <t>單井</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>350.3341396076783</v>
+        <v>390.6261650678609</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>74.5</v>
+        <v>32.45</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.1139452950509</v>
+        <v>42.09742926204422</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.22385783968103</v>
+        <v>25.67980493375254</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5903437878337202</v>
+        <v>0.3911231247069854</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-1.077472119619855</v>
+        <v>-0.7390539447935676</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>3230</v>
+        <v>3714</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>錦明</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>349.2942091935849</v>
+        <v>390.5449983109327</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>29.9</v>
+        <v>67.2</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>41.09808188803265</v>
+        <v>48.803609520141</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>24.15267080948569</v>
+        <v>16.21749340858833</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7132367671689233</v>
+        <v>0.4950649985522865</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.173767301550658</v>
+        <v>-0.4914350395162428</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>3593</v>
+        <v>3219</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>力銘</t>
+          <t>倚強股份</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>341.575994808585</v>
+        <v>390.3341396076783</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>16.05</v>
+        <v>74.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>41.18578581774168</v>
+        <v>46.1139452950509</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>20.90301145269122</v>
+        <v>15.22385783968103</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.587549457252201</v>
+        <v>0.5903437878337202</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0843518555689383</v>
+        <v>-1.077472119619855</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>3447</v>
+        <v>3563</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>展達</t>
+          <t>牧德</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>339.0641248104874</v>
+        <v>390.1078203884244</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>40.2</v>
+        <v>715</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>53.68241798632428</v>
+        <v>38.20539897678859</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.27442449719013</v>
+        <v>28.73468919902918</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5463215565884642</v>
+        <v>0.4948351461813322</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0339952485797206</v>
+        <v>-7.07557053873299</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>3588</v>
+        <v>3694</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>通嘉</t>
+          <t>海華</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>331.3487093242004</v>
+        <v>380.7330834021102</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>60.3</v>
+        <v>60.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>52.1593288457997</v>
+        <v>42.65218138624478</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>17.8004838116111</v>
+        <v>22.68336638757079</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.9544845205755657</v>
+        <v>0.7305452681799839</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1334552471147116</v>
+        <v>-0.802639713363772</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>3232</v>
+        <v>3230</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>昱捷</t>
+          <t>錦明</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>313.2783162702032</v>
+        <v>369.2942091935849</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>22.8</v>
+        <v>29.9</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>51.94190578368397</v>
+        <v>41.09808188803265</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.49008584653225</v>
+        <v>24.15267080948569</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2786357029530816</v>
+        <v>0.7132367671689233</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.06603263702872809</v>
+        <v>0.173767301550658</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>3163</v>
+        <v>3363</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>301.1659661622617</v>
+        <v>367.5165371769962</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>893</v>
+        <v>712</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.89686642985412</v>
+        <v>41.70182813571506</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.73376170915408</v>
+        <v>20.73953138332413</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.125275051752122</v>
+        <v>0.7929977644448646</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-10.92557096672118</v>
+        <v>-16.15721640819562</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>3217</v>
+        <v>3380</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>優群</t>
+          <t>明泰</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>294.4720008103661</v>
+        <v>365.5888163627444</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>170</v>
+        <v>34.95</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>40.02664362754357</v>
+        <v>48.59324281119195</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>24.19276195799954</v>
+        <v>17.3735304449494</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3466796023567606</v>
+        <v>0.7190149258182617</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-2.619201081261745</v>
+        <v>-0.2107163923609641</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>3373</v>
+        <v>3416</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>熱映</t>
+          <t>融程電</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>292.9918317507862</v>
+        <v>362.5467921930241</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>16.75</v>
+        <v>176</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.47534894461533</v>
+        <v>52.06296708975356</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>28.65508201362608</v>
+        <v>17.87939687907937</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.5541757702768983</v>
+        <v>0.3697577894850776</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0005488934979282</v>
+        <v>-1.289376063574811</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>3591</v>
+        <v>3191</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>艾笛森</t>
+          <t>雲嘉南</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>291.3911733635844</v>
+        <v>359.2716278551086</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>23.95</v>
+        <v>19.35</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>50.59149323886047</v>
+        <v>52.18343929384298</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>26.60411993731924</v>
+        <v>14.89285229231896</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.9554900518063402</v>
+        <v>0.4069120254139642</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.145687132093464</v>
+        <v>-0.4923849567954264</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>3272</v>
+        <v>3531</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>東碩</t>
+          <t>先益</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>288.9423480553023</v>
+        <v>353.823234755872</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>16.7</v>
+        <v>22.65</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>44.09063525676175</v>
+        <v>51.56538337420048</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.51437645041667</v>
+        <v>8.97730249049963</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.7373220220098851</v>
+        <v>0.8968961786617188</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.027271062597194</v>
+        <v>-0.3363975739781717</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>3708</v>
+        <v>3376</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>上緯投控</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>287.3339624498466</v>
+        <v>351.0884935582716</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>116.5</v>
+        <v>205</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,16 +7230,16 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45.01688292992419</v>
+        <v>47.12031839361605</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>11.1426659556077</v>
+        <v>17.96166975510926</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.6591632034347823</v>
+        <v>0.3715033286847038</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.6786837905716416</v>
+        <v>-2.529157980788407</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>3150</v>
+        <v>3521</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>鈺寶-創</t>
+          <t>鴻翊</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>280.4927500051744</v>
+        <v>344.7926227548789</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18.8</v>
+        <v>12.55</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>47.69384664889617</v>
+        <v>45.78951621805393</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>18.00272688280357</v>
+        <v>21.14979611772156</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.6594809246915331</v>
+        <v>0.3967401189629114</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.1228462839595109</v>
+        <v>0.08299499880307171</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>3686</v>
+        <v>3593</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>達能</t>
+          <t>力銘</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>279.2523069188151</v>
+        <v>341.575994808585</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>17.25</v>
+        <v>16.05</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.50130906539215</v>
+        <v>41.18578581774168</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>15.77859486224316</v>
+        <v>20.90301145269122</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.5345207206659371</v>
+        <v>0.587549457252201</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0380456214303241</v>
+        <v>-0.0843518555689383</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>3669</v>
+        <v>3447</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>圓展</t>
+          <t>展達</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>267.0409789233905</v>
+        <v>339.0641248104874</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>35.45</v>
+        <v>40.2</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>39.79369985292337</v>
+        <v>53.68241798632428</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>19.84160919334376</v>
+        <v>19.27442449719013</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.4646422518836738</v>
+        <v>0.5463215565884642</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.4226112799461726</v>
+        <v>0.0339952485797206</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>3325</v>
+        <v>3492</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>旭品</t>
+          <t>長盛</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>266.3651299908893</v>
+        <v>337.4923645861402</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>12.6</v>
+        <v>22.9</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,16 +7442,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>48.92517323645717</v>
+        <v>51.56562642647968</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>15.88798778327328</v>
+        <v>12.64078260122649</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.3361536015547204</v>
+        <v>0.4411662708023957</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0359395775507352</v>
+        <v>0.0227506340110963</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>3434</v>
+        <v>3588</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>哲固</t>
+          <t>通嘉</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>253.5394344463157</v>
+        <v>331.3487093242004</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>29.9</v>
+        <v>60.3</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>46.34828158007306</v>
+        <v>52.1593288457997</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>24.59792801352621</v>
+        <v>17.8004838116111</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.2950075906794966</v>
+        <v>0.9544845205755657</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.3055061322015669</v>
+        <v>-0.1334552471147116</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>3259</v>
+        <v>3232</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>鑫創</t>
+          <t>昱捷</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>248.4806962352928</v>
+        <v>313.2783162702032</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>16.55</v>
+        <v>22.8</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>46.24881306805764</v>
+        <v>51.94190578368397</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>16.91613593559972</v>
+        <v>19.49008584653225</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.2902953927214183</v>
+        <v>0.2786357029530816</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0259804388605431</v>
+        <v>-0.06603263702872809</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3622</v>
+        <v>3548</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>兆利</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>247.0381518976376</v>
+        <v>299.917279894966</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>55.7</v>
+        <v>89.2</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>47.14882510458874</v>
+        <v>40.10981290760611</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>16.25366220919533</v>
+        <v>13.71127132915182</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.3063182824452596</v>
+        <v>0.4207279728466553</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.2688413337275845</v>
+        <v>-0.7845150662078062</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>3297</v>
+        <v>3373</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>杭特</t>
+          <t>熱映</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>241.288766858734</v>
+        <v>292.9918317507862</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>31.6</v>
+        <v>16.75</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>49.23205782430784</v>
+        <v>46.47534894461533</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>15.74588175901761</v>
+        <v>28.65508201362608</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.3003853561719568</v>
+        <v>0.5541757702768983</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>0</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.0273084216678758</v>
+        <v>0.0005488934979282</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3323</v>
+        <v>3591</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>加百裕</t>
+          <t>艾笛森</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>239.9674741866257</v>
+        <v>291.3911733635844</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>35.5</v>
+        <v>23.95</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,16 +7707,16 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>48.03738652904139</v>
+        <v>50.59149323886047</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>20.386600364707</v>
+        <v>26.60411993731924</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.2476566166056936</v>
+        <v>0.9554900518063402</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.2908680958297585</v>
+        <v>-0.145687132093464</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>3437</v>
+        <v>3708</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>榮創</t>
+          <t>上緯投控</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>233.3402239173653</v>
+        <v>287.3339624498466</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>21.45</v>
+        <v>116.5</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>40.65420039629564</v>
+        <v>45.01688292992419</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>16.35499681992716</v>
+        <v>11.1426659556077</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.5678352186233746</v>
+        <v>0.6591632034347823</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.1525603981743074</v>
+        <v>-0.6786837905716416</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3543</v>
+        <v>3150</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>州巧</t>
+          <t>鈺寶-創</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>226.8898020007949</v>
+        <v>280.4927500051744</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>30.95</v>
+        <v>18.8</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>27.84418993814589</v>
+        <v>47.69384664889617</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>24.7632914321358</v>
+        <v>18.00272688280357</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.487906063508107</v>
+        <v>0.6594809246915331</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.1178890237711227</v>
+        <v>-0.1228462839595109</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>3178</v>
+        <v>3686</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>公準</t>
+          <t>達能</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>224.454443056986</v>
+        <v>279.2523069188151</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>17.25</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>46.94856522747758</v>
+        <v>49.50130906539215</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>18.70856235029699</v>
+        <v>15.77859486224316</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.6987405493872091</v>
+        <v>0.5345207206659371</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.4057573655740198</v>
+        <v>0.0380456214303241</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>3432</v>
+        <v>3259</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>台端</t>
+          <t>鑫創</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>215.5186659314057</v>
+        <v>268.4806962352928</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>18.7</v>
+        <v>16.55</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>49.81108312809998</v>
+        <v>46.24881306805764</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>15.60064443474195</v>
+        <v>16.91613593559972</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.7182726565644408</v>
+        <v>0.2902953927214183</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.0255891375339546</v>
+        <v>-0.0259804388605431</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>3518</v>
+        <v>3669</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>柏騰</t>
+          <t>圓展</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>189.1690883776571</v>
+        <v>267.0409789233905</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>28.35</v>
+        <v>35.45</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,16 +7972,16 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>40.0043264962312</v>
+        <v>39.79369985292337</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>26.44168163772412</v>
+        <v>19.84160919334376</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.3671918567180512</v>
+        <v>0.4646422518836738</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.5357075797592485</v>
+        <v>-0.4226112799461726</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>3466</v>
+        <v>3217</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>德晉</t>
+          <t>優群</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>185.1422948649402</v>
+        <v>264.4720008103661</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>33.2</v>
+        <v>170</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>46.77965860156392</v>
+        <v>40.02664362754357</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>15.51569526977725</v>
+        <v>24.19276195799954</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.5865094093107445</v>
+        <v>0.3466796023567606</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.269376121406959</v>
+        <v>-2.619201081261745</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>3494</v>
+        <v>3178</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>誠研</t>
+          <t>公準</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>179.7783449975784</v>
+        <v>264.454443056986</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,16 +8078,16 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>51.3842866971652</v>
+        <v>46.94856522747758</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>9.93861066824031</v>
+        <v>18.70856235029699</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.7554774250078164</v>
+        <v>0.6987405493872091</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.0010518427949772</v>
+        <v>-0.4057573655740198</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>3354</v>
+        <v>3297</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>律勝</t>
+          <t>杭特</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>174.6668466011377</v>
+        <v>261.2887668587339</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>28</v>
+        <v>31.6</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>42.58820440898489</v>
+        <v>49.23205782430784</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>22.65824577219858</v>
+        <v>15.74588175901761</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.2666424794186534</v>
+        <v>0.3003853561719568</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.393869331615136</v>
+        <v>0.0273084216678758</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>3645</v>
+        <v>3272</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>達邁</t>
+          <t>東碩</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>172.897505384717</v>
+        <v>258.9423480553023</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>94.3</v>
+        <v>16.7</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,13 +8184,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>44.76141668115796</v>
+        <v>44.09063525676175</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>17.28911921160433</v>
+        <v>19.51437645041667</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>0.3855160612988082</v>
+        <v>0.7373220220098851</v>
       </c>
       <c r="K146" s="2" t="n">
         <v>2</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-1.143135972137831</v>
+        <v>-0.027271062597194</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>3712</v>
+        <v>3622</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>永崴投控</t>
+          <t>洋華</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>167.3457950524</v>
+        <v>247.0381518976376</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>17.65</v>
+        <v>55.7</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>48.9575586329334</v>
+        <v>47.14882510458874</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>6.606520249921859</v>
+        <v>16.25366220919533</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.4465838461045091</v>
+        <v>0.3063182824452596</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,62 +8255,857 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0357043505935522</v>
+        <v>-0.2688413337275845</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
+        <v>3323</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>加百裕</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>239.9674741866257</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>48.03738652904139</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>20.386600364707</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>0.2476566166056936</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>-0.2908680958297585</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>旭品</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>236.3651299908893</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>48.92517323645717</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>15.88798778327328</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>0.3361536015547204</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>-0.0359395775507352</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>3437</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>榮創</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>233.3402239173653</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>40.65420039629564</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>16.35499681992716</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.5678352186233746</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>-0.1525603981743074</v>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>3499</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>環天科</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>232.6041086458162</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>39.96191391423687</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>28.77575316617963</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>0.4727776667872108</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>0.0224886597045517</v>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>3543</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>州巧</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>226.8898020007949</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>27.84418993814589</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>24.7632914321358</v>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.487906063508107</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>-0.1178890237711227</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>3466</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>德晉</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>225.1422948649402</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>46.77965860156392</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>15.51569526977725</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.5865094093107445</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>0.269376121406959</v>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>3434</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>哲固</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>223.5394344463157</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>46.34828158007306</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>24.59792801352621</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>0.2950075906794966</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>-0.3055061322015669</v>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>3432</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>台端</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>215.5186659314057</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>49.81108312809998</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>15.60064443474195</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0.7182726565644408</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>-0.0255891375339546</v>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>3354</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>律勝</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>214.6668466011377</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>42.58820440898489</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>22.65824577219858</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>0.2666424794186534</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>-0.393869331615136</v>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>3518</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>柏騰</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>189.1690883776571</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>40.0043264962312</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>26.44168163772412</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>0.3671918567180512</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>-0.5357075797592485</v>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>3494</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>誠研</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>179.7783449975784</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>51.3842866971652</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>9.93861066824031</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>0.7554774250078164</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>0.0010518427949772</v>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>3645</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>達邁</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>172.897505384717</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>44.76141668115796</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>17.28911921160433</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0.3855160612988082</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>-1.143135972137831</v>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>3712</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>永崴投控</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>167.3457950524</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>48.9575586329334</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>6.606520249921859</v>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>0.4465838461045091</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N160" s="2" t="n">
+        <v>0.0357043505935522</v>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
         <v>3224</v>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>三顧</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>87.47284242779982</v>
-      </c>
-      <c r="E148" s="2" t="n">
+      <c r="C161" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>127.4728424277998</v>
+      </c>
+      <c r="E161" s="2" t="n">
         <v>38.35</v>
       </c>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G148" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H148" s="2" t="n">
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H161" s="2" t="n">
         <v>43.64760025423576</v>
       </c>
-      <c r="I148" s="2" t="n">
+      <c r="I161" s="2" t="n">
         <v>19.36168287094669</v>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J161" s="2" t="n">
         <v>0.4216337751348695</v>
       </c>
-      <c r="K148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N148" s="2" t="n">
+      <c r="K161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N161" s="2" t="n">
         <v>0.1764561508323461</v>
       </c>
-      <c r="O148" s="2" t="inlineStr">
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>3508</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>位速</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>94.3152664259444</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>40.95801977293324</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>13.652039859861</v>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>0.8610637429147853</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N162" s="2" t="n">
+        <v>0.204298167090474</v>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>3540</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>曜越</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>88.00124769555562</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>43.23171639877997</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>15.09113575186908</v>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>1.231479112836486</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N163" s="2" t="n">
+        <v>-0.0761458543487111</v>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
